--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/55.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/55.xlsx
@@ -426,13 +426,13 @@
         <v>-19.30915700427809</v>
       </c>
       <c r="E2">
-        <v>-36.37093693721592</v>
+        <v>-34.78527817800812</v>
       </c>
       <c r="F2">
-        <v>-5.566242246483078</v>
+        <v>-4.873581305079798</v>
       </c>
       <c r="G2">
-        <v>-23.49290851264207</v>
+        <v>-22.82722732615095</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.94014021065674</v>
       </c>
       <c r="E3">
-        <v>-36.70388619591887</v>
+        <v>-34.56942620019551</v>
       </c>
       <c r="F3">
-        <v>-5.995556078494964</v>
+        <v>-4.688138836452088</v>
       </c>
       <c r="G3">
-        <v>-22.8271760126951</v>
+        <v>-22.87329025678438</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.53663175043276</v>
       </c>
       <c r="E4">
-        <v>-37.02618448375578</v>
+        <v>-35.3835077083174</v>
       </c>
       <c r="F4">
-        <v>-5.623692839336835</v>
+        <v>-4.560310977423887</v>
       </c>
       <c r="G4">
-        <v>-22.88494172180984</v>
+        <v>-22.32605542387008</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.11342610252076</v>
       </c>
       <c r="E5">
-        <v>-37.11024428252316</v>
+        <v>-35.5997627203167</v>
       </c>
       <c r="F5">
-        <v>-5.586586949895834</v>
+        <v>-4.743953403685316</v>
       </c>
       <c r="G5">
-        <v>-21.91465061915931</v>
+        <v>-21.84042156707777</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.68899326841313</v>
       </c>
       <c r="E6">
-        <v>-36.96246885446786</v>
+        <v>-35.73186283559445</v>
       </c>
       <c r="F6">
-        <v>-5.715653218191219</v>
+        <v>-4.761588517323514</v>
       </c>
       <c r="G6">
-        <v>-22.37689050589836</v>
+        <v>-21.79223326620814</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.27868021601819</v>
       </c>
       <c r="E7">
-        <v>-37.66383211606483</v>
+        <v>-35.85903823538886</v>
       </c>
       <c r="F7">
-        <v>-5.339933100405656</v>
+        <v>-4.678873547051775</v>
       </c>
       <c r="G7">
-        <v>-22.08089131868658</v>
+        <v>-21.83889540558416</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.89062855754269</v>
       </c>
       <c r="E8">
-        <v>-37.45704161474157</v>
+        <v>-36.73115440215606</v>
       </c>
       <c r="F8">
-        <v>-5.780367764800125</v>
+        <v>-4.61517706398091</v>
       </c>
       <c r="G8">
-        <v>-21.60424228248785</v>
+        <v>-21.31493867362925</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.52225102656164</v>
       </c>
       <c r="E9">
-        <v>-39.49941735575596</v>
+        <v>-37.14495730002896</v>
       </c>
       <c r="F9">
-        <v>-5.994137085133969</v>
+        <v>-4.772788044609364</v>
       </c>
       <c r="G9">
-        <v>-21.7455446424678</v>
+        <v>-21.05778211722975</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.2066209534774</v>
       </c>
       <c r="E10">
-        <v>-38.80946358442131</v>
+        <v>-37.76785569249503</v>
       </c>
       <c r="F10">
-        <v>-5.673111581853048</v>
+        <v>-4.504870832256724</v>
       </c>
       <c r="G10">
-        <v>-21.21064821277836</v>
+        <v>-20.84046797639537</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.96377415103102</v>
       </c>
       <c r="E11">
-        <v>-38.8707949721442</v>
+        <v>-37.91469825490475</v>
       </c>
       <c r="F11">
-        <v>-5.593331517289427</v>
+        <v>-4.520058948587054</v>
       </c>
       <c r="G11">
-        <v>-21.08542186193712</v>
+        <v>-20.21729253935573</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.80911331453188</v>
       </c>
       <c r="E12">
-        <v>-39.7945787631019</v>
+        <v>-38.09109590292553</v>
       </c>
       <c r="F12">
-        <v>-5.863493605303653</v>
+        <v>-4.732275908408051</v>
       </c>
       <c r="G12">
-        <v>-20.59323146970429</v>
+        <v>-19.80085736069804</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.73674214673059</v>
       </c>
       <c r="E13">
-        <v>-39.94888198643926</v>
+        <v>-38.60398407632326</v>
       </c>
       <c r="F13">
-        <v>-5.342583047727212</v>
+        <v>-4.459929415552643</v>
       </c>
       <c r="G13">
-        <v>-20.23606167729063</v>
+        <v>-20.12566491519255</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.77247283267485</v>
       </c>
       <c r="E14">
-        <v>-40.93619800348758</v>
+        <v>-39.60186955170549</v>
       </c>
       <c r="F14">
-        <v>-5.538816658511192</v>
+        <v>-4.449419918313326</v>
       </c>
       <c r="G14">
-        <v>-20.22573774102641</v>
+        <v>-19.5857050061008</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.91981836361228</v>
       </c>
       <c r="E15">
-        <v>-40.29306865339225</v>
+        <v>-39.52315788074117</v>
       </c>
       <c r="F15">
-        <v>-5.127064215438656</v>
+        <v>-4.314236985115669</v>
       </c>
       <c r="G15">
-        <v>-20.10979415987729</v>
+        <v>-19.17011898237393</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-16.16998438891683</v>
       </c>
       <c r="E16">
-        <v>-41.39719212899442</v>
+        <v>-40.22570533829115</v>
       </c>
       <c r="F16">
-        <v>-5.207510287394127</v>
+        <v>-4.407447370380877</v>
       </c>
       <c r="G16">
-        <v>-19.91132695479798</v>
+        <v>-18.75429790991378</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.48696549613329</v>
       </c>
       <c r="E17">
-        <v>-42.27864600916543</v>
+        <v>-40.37223996446835</v>
       </c>
       <c r="F17">
-        <v>-5.041267718428503</v>
+        <v>-4.151297945352409</v>
       </c>
       <c r="G17">
-        <v>-19.52468337544819</v>
+        <v>-18.73688775092275</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.85776795677343</v>
       </c>
       <c r="E18">
-        <v>-42.69116282042015</v>
+        <v>-40.77667118538238</v>
       </c>
       <c r="F18">
-        <v>-4.952661399188053</v>
+        <v>-3.959467107314308</v>
       </c>
       <c r="G18">
-        <v>-19.35074234699657</v>
+        <v>-18.59293529923862</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-17.25013806320004</v>
       </c>
       <c r="E19">
-        <v>-42.59449575001542</v>
+        <v>-41.05995666964321</v>
       </c>
       <c r="F19">
-        <v>-4.422619747730553</v>
+        <v>-3.977670480990827</v>
       </c>
       <c r="G19">
-        <v>-19.72982132978913</v>
+        <v>-18.58124907348499</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-17.62439230595905</v>
       </c>
       <c r="E20">
-        <v>-43.41003542676778</v>
+        <v>-41.8516018532941</v>
       </c>
       <c r="F20">
-        <v>-4.723841471512746</v>
+        <v>-4.05343296365087</v>
       </c>
       <c r="G20">
-        <v>-19.57450708581422</v>
+        <v>-18.48731896489925</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-17.92706404920873</v>
       </c>
       <c r="E21">
-        <v>-43.77935738870035</v>
+        <v>-41.70877831156618</v>
       </c>
       <c r="F21">
-        <v>-4.470628608927202</v>
+        <v>-3.620638331812421</v>
       </c>
       <c r="G21">
-        <v>-18.93475243671391</v>
+        <v>-18.27857582646605</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-18.13794601287524</v>
       </c>
       <c r="E22">
-        <v>-44.60078408166268</v>
+        <v>-42.98326524357392</v>
       </c>
       <c r="F22">
-        <v>-4.715216510114797</v>
+        <v>-3.637902336854165</v>
       </c>
       <c r="G22">
-        <v>-19.08608740495061</v>
+        <v>-18.1420323756988</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-18.23663587545825</v>
       </c>
       <c r="E23">
-        <v>-43.80698787285814</v>
+        <v>-42.74416408020593</v>
       </c>
       <c r="F23">
-        <v>-4.564878595282924</v>
+        <v>-3.592063798252851</v>
       </c>
       <c r="G23">
-        <v>-19.05521822306968</v>
+        <v>-18.23462171334114</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-18.20896177548985</v>
       </c>
       <c r="E24">
-        <v>-44.25500792033301</v>
+        <v>-42.61992086733149</v>
       </c>
       <c r="F24">
-        <v>-4.605233341677704</v>
+        <v>-3.531044598627834</v>
       </c>
       <c r="G24">
-        <v>-18.78581761399318</v>
+        <v>-18.06327615259231</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-18.03846302084961</v>
       </c>
       <c r="E25">
-        <v>-44.51825037863589</v>
+        <v>-43.10937645197653</v>
       </c>
       <c r="F25">
-        <v>-4.708055273917596</v>
+        <v>-3.619772687876495</v>
       </c>
       <c r="G25">
-        <v>-18.84812373631503</v>
+        <v>-17.97572380998798</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-17.74410679852714</v>
       </c>
       <c r="E26">
-        <v>-44.83785422443823</v>
+        <v>-43.23320304524227</v>
       </c>
       <c r="F26">
-        <v>-4.678456878248166</v>
+        <v>-3.745488210027556</v>
       </c>
       <c r="G26">
-        <v>-18.71647327185483</v>
+        <v>-18.09541161814202</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-17.34886560305847</v>
       </c>
       <c r="E27">
-        <v>-44.97686026257768</v>
+        <v>-43.06811299681863</v>
       </c>
       <c r="F27">
-        <v>-4.168423613037886</v>
+        <v>-3.548059265081336</v>
       </c>
       <c r="G27">
-        <v>-19.30847330155116</v>
+        <v>-18.35932334271441</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-16.87967332151723</v>
       </c>
       <c r="E28">
-        <v>-45.37471840346958</v>
+        <v>-43.24100560595748</v>
       </c>
       <c r="F28">
-        <v>-4.456477608585177</v>
+        <v>-3.6080860805578</v>
       </c>
       <c r="G28">
-        <v>-18.76142220391429</v>
+        <v>-18.22334102941608</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-16.3556087264823</v>
       </c>
       <c r="E29">
-        <v>-44.53570085322445</v>
+        <v>-43.29240378594454</v>
       </c>
       <c r="F29">
-        <v>-4.44443231818107</v>
+        <v>-3.701006537232029</v>
       </c>
       <c r="G29">
-        <v>-19.73675526742113</v>
+        <v>-18.595138467295</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-15.82147380396822</v>
       </c>
       <c r="E30">
-        <v>-44.81157096129772</v>
+        <v>-42.81628002877808</v>
       </c>
       <c r="F30">
-        <v>-4.605960648257362</v>
+        <v>-3.598914396674004</v>
       </c>
       <c r="G30">
-        <v>-18.47073809756581</v>
+        <v>-18.4968781651439</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-15.31705596623753</v>
       </c>
       <c r="E31">
-        <v>-45.11460964918</v>
+        <v>-42.78249761268086</v>
       </c>
       <c r="F31">
-        <v>-4.394898432595868</v>
+        <v>-3.399515594043926</v>
       </c>
       <c r="G31">
-        <v>-19.32793599877653</v>
+        <v>-18.54172281501886</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-14.87256014758918</v>
       </c>
       <c r="E32">
-        <v>-44.36048287268266</v>
+        <v>-42.66945784450139</v>
       </c>
       <c r="F32">
-        <v>-4.323725933714737</v>
+        <v>-3.446151850454136</v>
       </c>
       <c r="G32">
-        <v>-19.17999599499035</v>
+        <v>-18.61629450856372</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-14.49802271046067</v>
       </c>
       <c r="E33">
-        <v>-44.70497747586817</v>
+        <v>-42.3204257103602</v>
       </c>
       <c r="F33">
-        <v>-4.822580380824239</v>
+        <v>-3.560586665313873</v>
       </c>
       <c r="G33">
-        <v>-19.34050945073468</v>
+        <v>-18.68065316911992</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-14.21696295384462</v>
       </c>
       <c r="E34">
-        <v>-43.6710521400959</v>
+        <v>-42.10475487150789</v>
       </c>
       <c r="F34">
-        <v>-4.509438450115761</v>
+        <v>-3.625979644825672</v>
       </c>
       <c r="G34">
-        <v>-19.03831623281893</v>
+        <v>-18.70730802652936</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-14.0403804268429</v>
       </c>
       <c r="E35">
-        <v>-44.19279348017863</v>
+        <v>-41.96009050509586</v>
       </c>
       <c r="F35">
-        <v>-4.531639524878191</v>
+        <v>-3.514074664014084</v>
       </c>
       <c r="G35">
-        <v>-19.01563734060215</v>
+        <v>-19.18414907436937</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-13.96373568488532</v>
       </c>
       <c r="E36">
-        <v>-43.4583383947706</v>
+        <v>-41.32813969308846</v>
       </c>
       <c r="F36">
-        <v>-4.64507781375236</v>
+        <v>-3.515047995712373</v>
       </c>
       <c r="G36">
-        <v>-19.45499970239207</v>
+        <v>-19.09506063863481</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-13.96275998857704</v>
       </c>
       <c r="E37">
-        <v>-42.57360137094403</v>
+        <v>-41.04240430438948</v>
       </c>
       <c r="F37">
-        <v>-4.651468668264959</v>
+        <v>-3.701264987861702</v>
       </c>
       <c r="G37">
-        <v>-19.04285830129881</v>
+        <v>-18.80510154175943</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-14.02767825362308</v>
       </c>
       <c r="E38">
-        <v>-42.2358224947119</v>
+        <v>-41.0105985671966</v>
       </c>
       <c r="F38">
-        <v>-4.348697069072128</v>
+        <v>-3.427002481203619</v>
       </c>
       <c r="G38">
-        <v>-19.71717670110188</v>
+        <v>-19.36426095970618</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-14.14440064743787</v>
       </c>
       <c r="E39">
-        <v>-41.11720563804818</v>
+        <v>-40.3724437457987</v>
       </c>
       <c r="F39">
-        <v>-4.408035511236865</v>
+        <v>-3.331048543100338</v>
       </c>
       <c r="G39">
-        <v>-19.84399376907474</v>
+        <v>-18.73396453921157</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-14.29024703194934</v>
       </c>
       <c r="E40">
-        <v>-40.79228309952382</v>
+        <v>-39.52952491519596</v>
       </c>
       <c r="F40">
-        <v>-4.470939246703251</v>
+        <v>-3.542258208159531</v>
       </c>
       <c r="G40">
-        <v>-19.04716366577263</v>
+        <v>-19.01256349906894</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-14.43201859558939</v>
       </c>
       <c r="E41">
-        <v>-40.98553572780116</v>
+        <v>-39.87842798782793</v>
       </c>
       <c r="F41">
-        <v>-4.703312042169166</v>
+        <v>-3.373138719203984</v>
       </c>
       <c r="G41">
-        <v>-20.03995820172636</v>
+        <v>-19.01458293184789</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-14.55490878712957</v>
       </c>
       <c r="E42">
-        <v>-41.27354667468899</v>
+        <v>-39.83255228189322</v>
       </c>
       <c r="F42">
-        <v>-4.247331406726358</v>
+        <v>-3.519862467057444</v>
       </c>
       <c r="G42">
-        <v>-18.67452369405396</v>
+        <v>-19.68715998469731</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-14.64889543441366</v>
       </c>
       <c r="E43">
-        <v>-40.62310610330827</v>
+        <v>-39.32409295607499</v>
       </c>
       <c r="F43">
-        <v>-4.157536380262892</v>
+        <v>-3.370149141247281</v>
       </c>
       <c r="G43">
-        <v>-19.9186962291684</v>
+        <v>-18.82128679890093</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-14.70158643616441</v>
       </c>
       <c r="E44">
-        <v>-40.09373881299662</v>
+        <v>-38.52262551230146</v>
       </c>
       <c r="F44">
-        <v>-4.487141284734607</v>
+        <v>-3.444828119344462</v>
       </c>
       <c r="G44">
-        <v>-19.94425529600434</v>
+        <v>-19.11805072213228</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-14.69631938741791</v>
       </c>
       <c r="E45">
-        <v>-38.9981492466619</v>
+        <v>-38.42548068788891</v>
       </c>
       <c r="F45">
-        <v>-4.322888454270507</v>
+        <v>-3.380073811100222</v>
       </c>
       <c r="G45">
-        <v>-20.62866092806557</v>
+        <v>-19.1509592000654</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-14.6347459393312</v>
       </c>
       <c r="E46">
-        <v>-39.70441231713518</v>
+        <v>-38.22175596346884</v>
       </c>
       <c r="F46">
-        <v>-4.488382179104001</v>
+        <v>-3.388832139650021</v>
       </c>
       <c r="G46">
-        <v>-19.48987961019383</v>
+        <v>-19.4342607898613</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-14.52743405477172</v>
       </c>
       <c r="E47">
-        <v>-39.35830104872893</v>
+        <v>-36.86402435801512</v>
       </c>
       <c r="F47">
-        <v>-4.331538266690539</v>
+        <v>-3.216144043923213</v>
       </c>
       <c r="G47">
-        <v>-20.377547772548</v>
+        <v>-19.12125864075983</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-14.38186444634211</v>
       </c>
       <c r="E48">
-        <v>-39.3591093813393</v>
+        <v>-37.40686838697358</v>
       </c>
       <c r="F48">
-        <v>-4.305187071240084</v>
+        <v>-3.436165881413388</v>
       </c>
       <c r="G48">
-        <v>-20.14695834410114</v>
+        <v>-19.19609021212952</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-14.19934584554125</v>
       </c>
       <c r="E49">
-        <v>-38.91382906063908</v>
+        <v>-36.75410470842693</v>
       </c>
       <c r="F49">
-        <v>-4.15061785571471</v>
+        <v>-3.418021321822467</v>
       </c>
       <c r="G49">
-        <v>-21.00854602869694</v>
+        <v>-19.34077926019613</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.99274577081386</v>
       </c>
       <c r="E50">
-        <v>-38.07694668588857</v>
+        <v>-36.22018630173758</v>
       </c>
       <c r="F50">
-        <v>-4.135962379624382</v>
+        <v>-3.321854493296667</v>
       </c>
       <c r="G50">
-        <v>-19.90038891233623</v>
+        <v>-19.41476498718054</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.7805211896531</v>
       </c>
       <c r="E51">
-        <v>-37.29556076010205</v>
+        <v>-36.30257735783313</v>
       </c>
       <c r="F51">
-        <v>-4.409418884799541</v>
+        <v>-3.162102182931977</v>
       </c>
       <c r="G51">
-        <v>-19.70606319972655</v>
+        <v>-19.81507946433475</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.57272604095915</v>
       </c>
       <c r="E52">
-        <v>-37.54710164156911</v>
+        <v>-36.15045233049346</v>
       </c>
       <c r="F52">
-        <v>-3.866433992673298</v>
+        <v>-3.039265237505643</v>
       </c>
       <c r="G52">
-        <v>-20.42477601521124</v>
+        <v>-19.57647189459178</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.36948253883006</v>
       </c>
       <c r="E53">
-        <v>-37.05922196587874</v>
+        <v>-35.27734442791859</v>
       </c>
       <c r="F53">
-        <v>-4.091112083334608</v>
+        <v>-3.354571692237636</v>
       </c>
       <c r="G53">
-        <v>-20.45452126688159</v>
+        <v>-19.61928718005117</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.17843655272859</v>
       </c>
       <c r="E54">
-        <v>-36.46381141063923</v>
+        <v>-35.46589650017595</v>
       </c>
       <c r="F54">
-        <v>-4.160237686363422</v>
+        <v>-3.389569386638513</v>
       </c>
       <c r="G54">
-        <v>-20.53212707541319</v>
+        <v>-19.59036956476563</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.01293415784979</v>
       </c>
       <c r="E55">
-        <v>-36.2397470452137</v>
+        <v>-34.8545751515105</v>
       </c>
       <c r="F55">
-        <v>-4.155689949322052</v>
+        <v>-3.419767520307568</v>
       </c>
       <c r="G55">
-        <v>-19.85644804139348</v>
+        <v>-20.10791708055652</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.87618991359081</v>
       </c>
       <c r="E56">
-        <v>-37.14249607440579</v>
+        <v>-34.78955985018237</v>
       </c>
       <c r="F56">
-        <v>-4.120025419161922</v>
+        <v>-3.555743201109705</v>
       </c>
       <c r="G56">
-        <v>-20.37837375366005</v>
+        <v>-19.48678756066015</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.7622044891838</v>
       </c>
       <c r="E57">
-        <v>-36.78090874607833</v>
+        <v>-34.51405881274073</v>
       </c>
       <c r="F57">
-        <v>-4.186000740957889</v>
+        <v>-3.455166144531399</v>
       </c>
       <c r="G57">
-        <v>-19.91302691993239</v>
+        <v>-19.8291029352391</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.67054052469988</v>
       </c>
       <c r="E58">
-        <v>-35.96832616285297</v>
+        <v>-34.17488969498824</v>
       </c>
       <c r="F58">
-        <v>-4.235759942476652</v>
+        <v>-3.339551734490076</v>
       </c>
       <c r="G58">
-        <v>-20.25471660140442</v>
+        <v>-19.69076020297127</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.60864209041248</v>
       </c>
       <c r="E59">
-        <v>-36.26873833581082</v>
+        <v>-34.11567084038993</v>
       </c>
       <c r="F59">
-        <v>-4.207600420985885</v>
+        <v>-3.504860733392745</v>
       </c>
       <c r="G59">
-        <v>-19.73948481221826</v>
+        <v>-20.45373666758879</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.57376261443838</v>
       </c>
       <c r="E60">
-        <v>-36.2723316799359</v>
+        <v>-33.79309178716455</v>
       </c>
       <c r="F60">
-        <v>-4.084300418181388</v>
+        <v>-3.449375856385831</v>
       </c>
       <c r="G60">
-        <v>-20.65119746682415</v>
+        <v>-20.09069396738846</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.55544398640771</v>
       </c>
       <c r="E61">
-        <v>-36.21215958155898</v>
+        <v>-33.66277136217181</v>
       </c>
       <c r="F61">
-        <v>-4.280297944255571</v>
+        <v>-3.421602354104769</v>
       </c>
       <c r="G61">
-        <v>-20.71963803003028</v>
+        <v>-20.38263277049632</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.54766912794205</v>
       </c>
       <c r="E62">
-        <v>-33.87691157680952</v>
+        <v>-33.38087159095733</v>
       </c>
       <c r="F62">
-        <v>-4.144589826124538</v>
+        <v>-3.431965230313791</v>
       </c>
       <c r="G62">
-        <v>-21.07292951834468</v>
+        <v>-20.36920023197073</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.5552480857633</v>
       </c>
       <c r="E63">
-        <v>-35.82706947313171</v>
+        <v>-33.88933544524956</v>
       </c>
       <c r="F63">
-        <v>-4.481313720055913</v>
+        <v>-3.47545286222596</v>
       </c>
       <c r="G63">
-        <v>-21.29887425139994</v>
+        <v>-20.10061070655135</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.57340438421461</v>
       </c>
       <c r="E64">
-        <v>-34.9992825384256</v>
+        <v>-33.59266152758506</v>
       </c>
       <c r="F64">
-        <v>-4.31811954313259</v>
+        <v>-3.420300988914971</v>
       </c>
       <c r="G64">
-        <v>-21.49251302581022</v>
+        <v>-20.3505635158574</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.59145878260703</v>
       </c>
       <c r="E65">
-        <v>-34.94422535144034</v>
+        <v>-33.08136737703803</v>
       </c>
       <c r="F65">
-        <v>-4.220643894110367</v>
+        <v>-3.588144792070207</v>
       </c>
       <c r="G65">
-        <v>-21.22420324148891</v>
+        <v>-20.39919708510206</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.60170670512566</v>
       </c>
       <c r="E66">
-        <v>-35.19821840158256</v>
+        <v>-32.67639726771709</v>
       </c>
       <c r="F66">
-        <v>-4.100224124765402</v>
+        <v>-3.314648525259714</v>
       </c>
       <c r="G66">
-        <v>-21.53805289024844</v>
+        <v>-20.29995686147133</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.60858279544728</v>
       </c>
       <c r="E67">
-        <v>-34.99167243785571</v>
+        <v>-33.38526647498177</v>
       </c>
       <c r="F67">
-        <v>-4.426545380852421</v>
+        <v>-3.497883394758964</v>
       </c>
       <c r="G67">
-        <v>-21.27572526171659</v>
+        <v>-20.17016526833143</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.60742332637401</v>
       </c>
       <c r="E68">
-        <v>-34.44158964319598</v>
+        <v>-32.89491651672022</v>
       </c>
       <c r="F68">
-        <v>-4.573131619717016</v>
+        <v>-3.491453606978435</v>
       </c>
       <c r="G68">
-        <v>-21.57436129845039</v>
+        <v>-20.64123603529649</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.58859231116437</v>
       </c>
       <c r="E69">
-        <v>-34.99682584127644</v>
+        <v>-33.8183878429714</v>
       </c>
       <c r="F69">
-        <v>-4.228461197290586</v>
+        <v>-3.610917440340568</v>
       </c>
       <c r="G69">
-        <v>-21.31620164675249</v>
+        <v>-20.2088225085935</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.5447236015873</v>
       </c>
       <c r="E70">
-        <v>-34.46533922512921</v>
+        <v>-33.00079450325655</v>
       </c>
       <c r="F70">
-        <v>-4.617759913542838</v>
+        <v>-3.667895035407327</v>
       </c>
       <c r="G70">
-        <v>-20.51894448307581</v>
+        <v>-20.06711129623946</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.48234673688378</v>
       </c>
       <c r="E71">
-        <v>-34.52926316422148</v>
+        <v>-33.22217801206953</v>
       </c>
       <c r="F71">
-        <v>-4.662271407564867</v>
+        <v>-3.522241538238284</v>
       </c>
       <c r="G71">
-        <v>-20.76172334019826</v>
+        <v>-20.55249686211632</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.39941155285905</v>
       </c>
       <c r="E72">
-        <v>-34.81392304034364</v>
+        <v>-32.93353760729463</v>
       </c>
       <c r="F72">
-        <v>-4.330971663387024</v>
+        <v>-3.600721065979509</v>
       </c>
       <c r="G72">
-        <v>-20.27924443330488</v>
+        <v>-20.28983155793947</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.29008684961318</v>
       </c>
       <c r="E73">
-        <v>-35.94559095909747</v>
+        <v>-33.53289472763183</v>
       </c>
       <c r="F73">
-        <v>-4.69902275575747</v>
+        <v>-3.716700786045468</v>
       </c>
       <c r="G73">
-        <v>-20.76177961947243</v>
+        <v>-20.22369016861037</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.14946409564443</v>
       </c>
       <c r="E74">
-        <v>-36.00410337175057</v>
+        <v>-33.41113991122459</v>
       </c>
       <c r="F74">
-        <v>-4.933758883423572</v>
+        <v>-3.744484228735363</v>
       </c>
       <c r="G74">
-        <v>-20.75553262003983</v>
+        <v>-19.9879826367598</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.98758650283904</v>
       </c>
       <c r="E75">
-        <v>-35.33277747824648</v>
+        <v>-34.0485271562782</v>
       </c>
       <c r="F75">
-        <v>-4.598553386941529</v>
+        <v>-3.842413823094321</v>
       </c>
       <c r="G75">
-        <v>-20.37304212006905</v>
+        <v>-20.51493210188221</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.80552868677934</v>
       </c>
       <c r="E76">
-        <v>-35.45782223102028</v>
+        <v>-33.49955383775035</v>
       </c>
       <c r="F76">
-        <v>-4.558279820552223</v>
+        <v>-3.828031708246916</v>
       </c>
       <c r="G76">
-        <v>-19.9930361845255</v>
+        <v>-19.94905724230905</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.60130359396968</v>
       </c>
       <c r="E77">
-        <v>-35.04210831711614</v>
+        <v>-33.91790332352696</v>
       </c>
       <c r="F77">
-        <v>-4.632286164318331</v>
+        <v>-3.941174269958287</v>
       </c>
       <c r="G77">
-        <v>-19.5739029112533</v>
+        <v>-19.94335151707212</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.37274226190758</v>
       </c>
       <c r="E78">
-        <v>-35.38381338031292</v>
+        <v>-34.36055260082872</v>
       </c>
       <c r="F78">
-        <v>-4.674595029416316</v>
+        <v>-3.954293124516422</v>
       </c>
       <c r="G78">
-        <v>-20.1124972203101</v>
+        <v>-20.34685239430788</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.13306933331427</v>
       </c>
       <c r="E79">
-        <v>-36.31066747664784</v>
+        <v>-34.21548067175599</v>
       </c>
       <c r="F79">
-        <v>-4.955559856730449</v>
+        <v>-4.031816716274816</v>
       </c>
       <c r="G79">
-        <v>-20.08397852576205</v>
+        <v>-19.69686815949122</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.88618707237757</v>
       </c>
       <c r="E80">
-        <v>-36.16314564313696</v>
+        <v>-34.84583066820169</v>
       </c>
       <c r="F80">
-        <v>-5.088358748542849</v>
+        <v>-4.100959715019089</v>
       </c>
       <c r="G80">
-        <v>-20.2998492687413</v>
+        <v>-20.14124599777313</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.6335093340431</v>
       </c>
       <c r="E81">
-        <v>-36.28962592217119</v>
+        <v>-35.2104611310623</v>
       </c>
       <c r="F81">
-        <v>-4.464222843801353</v>
+        <v>-4.162471793248772</v>
       </c>
       <c r="G81">
-        <v>-20.05878527420819</v>
+        <v>-19.7678843271269</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.37461875771455</v>
       </c>
       <c r="E82">
-        <v>-37.56266374249647</v>
+        <v>-34.9656314480746</v>
       </c>
       <c r="F82">
-        <v>-4.675151692310997</v>
+        <v>-4.11805390474326</v>
       </c>
       <c r="G82">
-        <v>-20.13287693864985</v>
+        <v>-19.43842380087694</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.12555716958568</v>
       </c>
       <c r="E83">
-        <v>-37.43184518536289</v>
+        <v>-35.83500335959315</v>
       </c>
       <c r="F83">
-        <v>-5.238661043576402</v>
+        <v>-4.218397361713975</v>
       </c>
       <c r="G83">
-        <v>-19.19118729418586</v>
+        <v>-19.70859245651855</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.893005983985242</v>
       </c>
       <c r="E84">
-        <v>-37.60488723414399</v>
+        <v>-36.51828442447749</v>
       </c>
       <c r="F84">
-        <v>-5.185100464046192</v>
+        <v>-4.333093940672997</v>
       </c>
       <c r="G84">
-        <v>-19.62225177358159</v>
+        <v>-19.31810202325213</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.681088851634946</v>
       </c>
       <c r="E85">
-        <v>-39.03214902951149</v>
+        <v>-36.7989547149989</v>
       </c>
       <c r="F85">
-        <v>-5.063752923210092</v>
+        <v>-4.336585509275797</v>
       </c>
       <c r="G85">
-        <v>-18.76176981119591</v>
+        <v>-19.19463357209224</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.489760383569507</v>
       </c>
       <c r="E86">
-        <v>-39.82251491925522</v>
+        <v>-37.51893453324141</v>
       </c>
       <c r="F86">
-        <v>-4.988103926884233</v>
+        <v>-4.300637677463909</v>
       </c>
       <c r="G86">
-        <v>-19.34351046026603</v>
+        <v>-19.47642058730392</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.336873671242403</v>
       </c>
       <c r="E87">
-        <v>-40.45189582226327</v>
+        <v>-38.22886113918688</v>
       </c>
       <c r="F87">
-        <v>-5.498645809679833</v>
+        <v>-4.407685111825481</v>
       </c>
       <c r="G87">
-        <v>-19.71092639112373</v>
+        <v>-19.05498151906362</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.229753864401395</v>
       </c>
       <c r="E88">
-        <v>-39.99627473116654</v>
+        <v>-38.44661507608271</v>
       </c>
       <c r="F88">
-        <v>-5.446834742104335</v>
+        <v>-4.520680224139153</v>
       </c>
       <c r="G88">
-        <v>-18.9510800473136</v>
+        <v>-19.49516158560174</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.173205119675512</v>
       </c>
       <c r="E89">
-        <v>-42.07050149411388</v>
+        <v>-39.8587472397906</v>
       </c>
       <c r="F89">
-        <v>-5.249617030845829</v>
+        <v>-4.303446671326802</v>
       </c>
       <c r="G89">
-        <v>-19.46248484585636</v>
+        <v>-18.7317663369735</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.163465565161802</v>
       </c>
       <c r="E90">
-        <v>-42.21218612462886</v>
+        <v>-40.96932152661669</v>
       </c>
       <c r="F90">
-        <v>-5.775817542656547</v>
+        <v>-4.579017170113906</v>
       </c>
       <c r="G90">
-        <v>-18.8158260540339</v>
+        <v>-19.40223457231439</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.217032573955477</v>
       </c>
       <c r="E91">
-        <v>-43.26300946116076</v>
+        <v>-41.09175108565106</v>
       </c>
       <c r="F91">
-        <v>-5.253367878445705</v>
+        <v>-4.792870155555431</v>
       </c>
       <c r="G91">
-        <v>-18.89679372156063</v>
+        <v>-18.76861932991666</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.3376356004394</v>
       </c>
       <c r="E92">
-        <v>-44.37436490975318</v>
+        <v>-42.12085812507917</v>
       </c>
       <c r="F92">
-        <v>-5.159999275006562</v>
+        <v>-4.591569421368527</v>
       </c>
       <c r="G92">
-        <v>-19.47814538152988</v>
+        <v>-19.25385095542595</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.525678537459552</v>
       </c>
       <c r="E93">
-        <v>-44.69318306531519</v>
+        <v>-43.66303900533933</v>
       </c>
       <c r="F93">
-        <v>-5.686446640303314</v>
+        <v>-4.882535956704062</v>
       </c>
       <c r="G93">
-        <v>-19.36289039385293</v>
+        <v>-19.04227233473836</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.769035594640572</v>
       </c>
       <c r="E94">
-        <v>-46.88622566503878</v>
+        <v>-44.26686572952209</v>
       </c>
       <c r="F94">
-        <v>-5.87734390827846</v>
+        <v>-4.718406552982978</v>
       </c>
       <c r="G94">
-        <v>-19.7658781365301</v>
+        <v>-19.40464464946698</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.07576616016934</v>
       </c>
       <c r="E95">
-        <v>-47.28608991991607</v>
+        <v>-45.58030659494381</v>
       </c>
       <c r="F95">
-        <v>-5.778263711597014</v>
+        <v>-5.047968382349747</v>
       </c>
       <c r="G95">
-        <v>-19.43465805532601</v>
+        <v>-19.30408682871162</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.44514109551842</v>
       </c>
       <c r="E96">
-        <v>-48.13591467338051</v>
+        <v>-47.10558268173332</v>
       </c>
       <c r="F96">
-        <v>-6.01143588160663</v>
+        <v>-5.037964189226138</v>
       </c>
       <c r="G96">
-        <v>-19.22118083677165</v>
+        <v>-19.56458207028748</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.8637410221162</v>
       </c>
       <c r="E97">
-        <v>-48.96080564895872</v>
+        <v>-48.13404214937834</v>
       </c>
       <c r="F97">
-        <v>-5.87956310455056</v>
+        <v>-5.301766072321668</v>
       </c>
       <c r="G97">
-        <v>-19.80890860744955</v>
+        <v>-19.43172822252376</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.32278763593656</v>
       </c>
       <c r="E98">
-        <v>-51.00880235833512</v>
+        <v>-49.85051493724571</v>
       </c>
       <c r="F98">
-        <v>-6.309117163109258</v>
+        <v>-5.397478955510735</v>
       </c>
       <c r="G98">
-        <v>-21.15547962663918</v>
+        <v>-19.59128327533448</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.80796968081328</v>
       </c>
       <c r="E99">
-        <v>-52.42335046292609</v>
+        <v>-50.67487494924652</v>
       </c>
       <c r="F99">
-        <v>-6.607782545086411</v>
+        <v>-5.466730470384774</v>
       </c>
       <c r="G99">
-        <v>-20.07714555976899</v>
+        <v>-19.67166497630075</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.33681727660371</v>
       </c>
       <c r="E100">
-        <v>-52.91813266512266</v>
+        <v>-52.4062905692207</v>
       </c>
       <c r="F100">
-        <v>-6.202256939780719</v>
+        <v>-5.755945008663387</v>
       </c>
       <c r="G100">
-        <v>-19.98537723742039</v>
+        <v>-20.04108378720971</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.85622775481593</v>
       </c>
       <c r="E101">
-        <v>-54.58957883593177</v>
+        <v>-53.34147479349272</v>
       </c>
       <c r="F101">
-        <v>-6.892826667675631</v>
+        <v>-5.778799665306626</v>
       </c>
       <c r="G101">
-        <v>-20.2131510468861</v>
+        <v>-19.93908587914477</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.41499132249344</v>
       </c>
       <c r="E102">
-        <v>-56.49729813809108</v>
+        <v>-55.6299164908989</v>
       </c>
       <c r="F102">
-        <v>-6.967615404453683</v>
+        <v>-6.015491568410737</v>
       </c>
       <c r="G102">
-        <v>-20.32241063659144</v>
+        <v>-20.33132428045592</v>
       </c>
     </row>
   </sheetData>
